--- a/Externals/week12 - Latihan Anomaly.xlsx
+++ b/Externals/week12 - Latihan Anomaly.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kemenkeu-my.sharepoint.com/personal/teuku_radarma_kemenkeu_go_id/Documents/PKN STAN/TABK Genap/TABK-STAN/2024/slide/Week 12 - Analisis Data dan Sampling II/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kemenkeu-my.sharepoint.com/personal/teuku_radarma_kemenkeu_go_id/Documents/PKN STAN/Audit SI/Externals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{39B1036D-5CCA-42E4-A28C-7F3380E482CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DFF6EFF-EAFA-49AF-9670-80171B45CE22}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{39B1036D-5CCA-42E4-A28C-7F3380E482CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{247BC16E-9EA8-4742-98F4-6EF567A87358}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12096" xr2:uid="{039F10D1-0191-47E3-BDBD-318F99DAF265}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="25780" windowHeight="15460" xr2:uid="{039F10D1-0191-47E3-BDBD-318F99DAF265}"/>
   </bookViews>
   <sheets>
     <sheet name="master invoice" sheetId="2" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -2382,14 +2385,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2415,19 +2411,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -2451,7 +2444,7 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{A54C8224-72AA-4817-BAF5-EA8C9ED312C6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="8">
+  <queryTableRefresh nextId="10">
     <queryTableFields count="4">
       <queryTableField id="1" name="no_invoice" tableColumnId="1"/>
       <queryTableField id="2" name="tgl_invoice" tableColumnId="2"/>
@@ -2476,9 +2469,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2516,7 +2509,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2622,7 +2615,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2764,7 +2757,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2772,16 +2765,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0F298B-ACDE-4725-9832-C85C433B515D}">
-  <dimension ref="A1:J780"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E780"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2795,7 +2788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2809,7 +2802,7 @@
         <v>10251</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2823,7 +2816,7 @@
         <v>10250</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2837,7 +2830,7 @@
         <v>10248</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2851,7 +2844,7 @@
         <v>10253</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2865,7 +2858,7 @@
         <v>10261</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2879,7 +2872,7 @@
         <v>10258</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2893,7 +2886,7 @@
         <v>10265</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2907,7 +2900,7 @@
         <v>10269</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2921,7 +2914,7 @@
         <v>10257</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2934,11 +2927,9 @@
       <c r="D11">
         <v>10268</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -2951,11 +2942,9 @@
       <c r="D12">
         <v>10267</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -2968,11 +2957,9 @@
       <c r="D13">
         <v>10249</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -2985,11 +2972,9 @@
       <c r="D14">
         <v>10254</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -3002,11 +2987,9 @@
       <c r="D15">
         <v>10279</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3019,11 +3002,9 @@
       <c r="D16">
         <v>10259</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -3036,11 +3017,9 @@
       <c r="D17">
         <v>10262</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -3053,11 +3032,9 @@
       <c r="D18">
         <v>10271</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -3070,11 +3047,9 @@
       <c r="D19">
         <v>10266</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -3088,7 +3063,7 @@
         <v>10276</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -3102,7 +3077,7 @@
         <v>10260</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -3116,7 +3091,7 @@
         <v>10255</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -3130,7 +3105,7 @@
         <v>10256</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -3144,7 +3119,7 @@
         <v>10286</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -3158,7 +3133,7 @@
         <v>10272</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -3172,7 +3147,7 @@
         <v>10274</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -3186,7 +3161,7 @@
         <v>10281</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -3200,7 +3175,7 @@
         <v>10291</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -3214,7 +3189,7 @@
         <v>10288</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -3228,7 +3203,7 @@
         <v>10263</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -3242,7 +3217,7 @@
         <v>10297</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -3256,7 +3231,7 @@
         <v>10287</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -3270,7 +3245,7 @@
         <v>10273</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -3284,7 +3259,7 @@
         <v>10282</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -3298,7 +3273,7 @@
         <v>10298</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -3312,7 +3287,7 @@
         <v>10300</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -3326,7 +3301,7 @@
         <v>10296</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -3340,7 +3315,7 @@
         <v>10306</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -3354,7 +3329,7 @@
         <v>10275</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -3368,7 +3343,7 @@
         <v>10302</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -3382,7 +3357,7 @@
         <v>10283</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -3396,7 +3371,7 @@
         <v>10290</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -3410,7 +3385,7 @@
         <v>10280</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -3424,7 +3399,7 @@
         <v>10312</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -3438,7 +3413,7 @@
         <v>10285</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -3452,7 +3427,7 @@
         <v>10311</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -3466,7 +3441,7 @@
         <v>10294</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -3480,7 +3455,7 @@
         <v>10301</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -3494,7 +3469,7 @@
         <v>10314</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -3508,7 +3483,7 @@
         <v>10315</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -3522,7 +3497,7 @@
         <v>10321</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -3536,7 +3511,7 @@
         <v>10292</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -3550,7 +3525,7 @@
         <v>10307</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -3564,7 +3539,7 @@
         <v>10289</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -3578,7 +3553,7 @@
         <v>10299</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -3592,7 +3567,7 @@
         <v>10319</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -3606,7 +3581,7 @@
         <v>10304</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -3620,7 +3595,7 @@
         <v>10309</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -3634,7 +3609,7 @@
         <v>10308</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -3648,7 +3623,7 @@
         <v>10335</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -3662,7 +3637,7 @@
         <v>10320</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -3676,7 +3651,7 @@
         <v>10327</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -3690,7 +3665,7 @@
         <v>10331</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -3704,7 +3679,7 @@
         <v>10323</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -3718,7 +3693,7 @@
         <v>10333</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -3732,7 +3707,7 @@
         <v>10310</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -3746,7 +3721,7 @@
         <v>10313</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -3760,7 +3735,7 @@
         <v>10328</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -3774,7 +3749,7 @@
         <v>10329</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -3788,7 +3763,7 @@
         <v>10326</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -3802,7 +3777,7 @@
         <v>10342</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -3816,7 +3791,7 @@
         <v>10336</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -3830,7 +3805,7 @@
         <v>10334</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -3844,7 +3819,7 @@
         <v>10318</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -3858,7 +3833,7 @@
         <v>10317</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -3872,7 +3847,7 @@
         <v>10330</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -3886,7 +3861,7 @@
         <v>10316</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -3900,7 +3875,7 @@
         <v>10322</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -3914,7 +3889,7 @@
         <v>10343</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -3928,7 +3903,7 @@
         <v>10346</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -3942,7 +3917,7 @@
         <v>10347</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -3956,7 +3931,7 @@
         <v>10352</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -3970,7 +3945,7 @@
         <v>10337</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -3984,7 +3959,7 @@
         <v>10353</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -3998,7 +3973,7 @@
         <v>10325</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -4012,7 +3987,7 @@
         <v>10357</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -4026,7 +4001,7 @@
         <v>10340</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -4040,7 +4015,7 @@
         <v>10349</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -4054,7 +4029,7 @@
         <v>10354</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -4068,7 +4043,7 @@
         <v>10355</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -4082,7 +4057,7 @@
         <v>10345</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -4096,7 +4071,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -4110,7 +4085,7 @@
         <v>10338</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -4124,7 +4099,7 @@
         <v>10341</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -4138,7 +4113,7 @@
         <v>10332</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -4152,7 +4127,7 @@
         <v>10350</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -4166,7 +4141,7 @@
         <v>10344</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -4180,7 +4155,7 @@
         <v>10362</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>101</v>
       </c>
@@ -4194,7 +4169,7 @@
         <v>10371</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>102</v>
       </c>
@@ -4208,7 +4183,7 @@
         <v>10348</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>103</v>
       </c>
@@ -4222,7 +4197,7 @@
         <v>10368</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -4236,7 +4211,7 @@
         <v>10361</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -4250,7 +4225,7 @@
         <v>10356</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>106</v>
       </c>
@@ -4264,7 +4239,7 @@
         <v>10359</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -4278,7 +4253,7 @@
         <v>10375</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>108</v>
       </c>
@@ -4292,7 +4267,7 @@
         <v>10383</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>108</v>
       </c>
@@ -4306,7 +4281,7 @@
         <v>10376</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>109</v>
       </c>
@@ -4320,7 +4295,7 @@
         <v>10373</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>110</v>
       </c>
@@ -4334,7 +4309,7 @@
         <v>10366</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>111</v>
       </c>
@@ -4348,7 +4323,7 @@
         <v>10374</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>112</v>
       </c>
@@ -4362,7 +4337,7 @@
         <v>10364</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>113</v>
       </c>
@@ -4376,7 +4351,7 @@
         <v>10367</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -4390,7 +4365,7 @@
         <v>10377</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -4404,7 +4379,7 @@
         <v>10384</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -4418,7 +4393,7 @@
         <v>10365</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -4432,7 +4407,7 @@
         <v>10363</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -4446,7 +4421,7 @@
         <v>10393</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>119</v>
       </c>
@@ -4460,7 +4435,7 @@
         <v>10394</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>120</v>
       </c>
@@ -4474,7 +4449,7 @@
         <v>10379</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>121</v>
       </c>
@@ -4488,7 +4463,7 @@
         <v>10388</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>122</v>
       </c>
@@ -4502,7 +4477,7 @@
         <v>10382</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>123</v>
       </c>
@@ -4516,7 +4491,7 @@
         <v>10378</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>124</v>
       </c>
@@ -4530,7 +4505,7 @@
         <v>10380</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>125</v>
       </c>
@@ -4544,7 +4519,7 @@
         <v>10385</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>126</v>
       </c>
@@ -4558,7 +4533,7 @@
         <v>10369</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>127</v>
       </c>
@@ -4572,7 +4547,7 @@
         <v>10392</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>128</v>
       </c>
@@ -4586,7 +4561,7 @@
         <v>10386</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>129</v>
       </c>
@@ -4600,7 +4575,7 @@
         <v>10391</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>130</v>
       </c>
@@ -4614,7 +4589,7 @@
         <v>10411</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>131</v>
       </c>
@@ -4628,7 +4603,7 @@
         <v>10408</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>132</v>
       </c>
@@ -4642,7 +4617,7 @@
         <v>10390</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>133</v>
       </c>
@@ -4656,7 +4631,7 @@
         <v>10404</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>134</v>
       </c>
@@ -4670,7 +4645,7 @@
         <v>10381</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>135</v>
       </c>
@@ -4684,7 +4659,7 @@
         <v>10399</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>136</v>
       </c>
@@ -4698,7 +4673,7 @@
         <v>10406</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>137</v>
       </c>
@@ -4712,7 +4687,7 @@
         <v>10403</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>138</v>
       </c>
@@ -4726,7 +4701,7 @@
         <v>10410</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>139</v>
       </c>
@@ -4740,7 +4715,7 @@
         <v>10419</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>140</v>
       </c>
@@ -4754,7 +4729,7 @@
         <v>10389</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -4768,7 +4743,7 @@
         <v>10387</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>141</v>
       </c>
@@ -4782,7 +4757,7 @@
         <v>10398</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -4796,7 +4771,7 @@
         <v>10397</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -4810,7 +4785,7 @@
         <v>10405</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>140</v>
       </c>
@@ -4824,7 +4799,7 @@
         <v>10400</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>143</v>
       </c>
@@ -4838,7 +4813,7 @@
         <v>10395</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>144</v>
       </c>
@@ -4852,7 +4827,7 @@
         <v>10396</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>145</v>
       </c>
@@ -4866,7 +4841,7 @@
         <v>10401</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>146</v>
       </c>
@@ -4880,7 +4855,7 @@
         <v>10402</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>146</v>
       </c>
@@ -4894,7 +4869,7 @@
         <v>10441</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>147</v>
       </c>
@@ -4908,7 +4883,7 @@
         <v>10415</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>148</v>
       </c>
@@ -4922,7 +4897,7 @@
         <v>10422</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>149</v>
       </c>
@@ -4936,7 +4911,7 @@
         <v>10433</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>150</v>
       </c>
@@ -4950,7 +4925,7 @@
         <v>10409</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>151</v>
       </c>
@@ -4964,7 +4939,7 @@
         <v>10423</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>152</v>
       </c>
@@ -4978,7 +4953,7 @@
         <v>10429</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>153</v>
       </c>
@@ -4992,7 +4967,7 @@
         <v>10414</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>154</v>
       </c>
@@ -5006,7 +4981,7 @@
         <v>10430</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>155</v>
       </c>
@@ -5020,7 +4995,7 @@
         <v>10421</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>156</v>
       </c>
@@ -5034,7 +5009,7 @@
         <v>10412</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>157</v>
       </c>
@@ -5048,7 +5023,7 @@
         <v>10434</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>158</v>
       </c>
@@ -5062,7 +5037,7 @@
         <v>10418</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>159</v>
       </c>
@@ -5076,7 +5051,7 @@
         <v>10431</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>160</v>
       </c>
@@ -5090,7 +5065,7 @@
         <v>10432</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>161</v>
       </c>
@@ -5104,7 +5079,7 @@
         <v>10416</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>162</v>
       </c>
@@ -5118,7 +5093,7 @@
         <v>10435</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>163</v>
       </c>
@@ -5132,7 +5107,7 @@
         <v>10443</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>164</v>
       </c>
@@ -5146,7 +5121,7 @@
         <v>10428</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>165</v>
       </c>
@@ -5160,7 +5135,7 @@
         <v>10436</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>166</v>
       </c>
@@ -5174,7 +5149,7 @@
         <v>10446</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>167</v>
       </c>
@@ -5188,7 +5163,7 @@
         <v>10453</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>168</v>
       </c>
@@ -5202,7 +5177,7 @@
         <v>10426</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>169</v>
       </c>
@@ -5216,7 +5191,7 @@
         <v>10455</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>170</v>
       </c>
@@ -5230,7 +5205,7 @@
         <v>10463</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>171</v>
       </c>
@@ -5244,7 +5219,7 @@
         <v>10448</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>172</v>
       </c>
@@ -5258,7 +5233,7 @@
         <v>10420</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>173</v>
       </c>
@@ -5272,7 +5247,7 @@
         <v>10437</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>174</v>
       </c>
@@ -5286,7 +5261,7 @@
         <v>10451</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>175</v>
       </c>
@@ -5300,7 +5275,7 @@
         <v>10427</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>176</v>
       </c>
@@ -5314,7 +5289,7 @@
         <v>10457</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>177</v>
       </c>
@@ -5328,7 +5303,7 @@
         <v>10460</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>178</v>
       </c>
@@ -5342,7 +5317,7 @@
         <v>10439</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>179</v>
       </c>
@@ -5356,7 +5331,7 @@
         <v>10445</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>180</v>
       </c>
@@ -5370,7 +5345,7 @@
         <v>10464</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>180</v>
       </c>
@@ -5384,7 +5359,7 @@
         <v>10458</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>181</v>
       </c>
@@ -5398,7 +5373,7 @@
         <v>10452</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>182</v>
       </c>
@@ -5412,7 +5387,7 @@
         <v>10440</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>183</v>
       </c>
@@ -5426,7 +5401,7 @@
         <v>10444</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>184</v>
       </c>
@@ -5440,7 +5415,7 @@
         <v>10476</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>185</v>
       </c>
@@ -5454,7 +5429,7 @@
         <v>10459</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>186</v>
       </c>
@@ -5468,7 +5443,7 @@
         <v>10442</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>187</v>
       </c>
@@ -5482,7 +5457,7 @@
         <v>10465</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>188</v>
       </c>
@@ -5496,7 +5471,7 @@
         <v>10438</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>189</v>
       </c>
@@ -5510,7 +5485,7 @@
         <v>10475</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>190</v>
       </c>
@@ -5524,7 +5499,7 @@
         <v>10462</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>191</v>
       </c>
@@ -5538,7 +5513,7 @@
         <v>10469</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>192</v>
       </c>
@@ -5552,7 +5527,7 @@
         <v>10450</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>193</v>
       </c>
@@ -5566,7 +5541,7 @@
         <v>10456</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>194</v>
       </c>
@@ -5580,7 +5555,7 @@
         <v>10449</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>195</v>
       </c>
@@ -5594,7 +5569,7 @@
         <v>10470</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>196</v>
       </c>
@@ -5608,7 +5583,7 @@
         <v>10454</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>197</v>
       </c>
@@ -5622,7 +5597,7 @@
         <v>10468</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>198</v>
       </c>
@@ -5636,7 +5611,7 @@
         <v>10472</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>199</v>
       </c>
@@ -5650,7 +5625,7 @@
         <v>10467</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>200</v>
       </c>
@@ -5664,7 +5639,7 @@
         <v>10484</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>201</v>
       </c>
@@ -5678,7 +5653,7 @@
         <v>10447</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>202</v>
       </c>
@@ -5692,7 +5667,7 @@
         <v>10480</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>203</v>
       </c>
@@ -5706,7 +5681,7 @@
         <v>10489</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>204</v>
       </c>
@@ -5720,7 +5695,7 @@
         <v>10487</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>205</v>
       </c>
@@ -5734,7 +5709,7 @@
         <v>10488</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>206</v>
       </c>
@@ -5748,7 +5723,7 @@
         <v>10494</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>207</v>
       </c>
@@ -5762,7 +5737,7 @@
         <v>10481</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>208</v>
       </c>
@@ -5776,7 +5751,7 @@
         <v>10485</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>209</v>
       </c>
@@ -5790,7 +5765,7 @@
         <v>10466</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>210</v>
       </c>
@@ -5804,7 +5779,7 @@
         <v>10473</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>211</v>
       </c>
@@ -5818,7 +5793,7 @@
         <v>10491</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>212</v>
       </c>
@@ -5832,7 +5807,7 @@
         <v>10493</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>213</v>
       </c>
@@ -5846,7 +5821,7 @@
         <v>10479</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>214</v>
       </c>
@@ -5860,7 +5835,7 @@
         <v>10492</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>215</v>
       </c>
@@ -5874,7 +5849,7 @@
         <v>10471</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>216</v>
       </c>
@@ -5888,7 +5863,7 @@
         <v>10490</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>217</v>
       </c>
@@ -5902,7 +5877,7 @@
         <v>10497</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>218</v>
       </c>
@@ -5916,7 +5891,7 @@
         <v>10486</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>219</v>
       </c>
@@ -5930,7 +5905,7 @@
         <v>10483</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>220</v>
       </c>
@@ -5944,7 +5919,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>221</v>
       </c>
@@ -5958,7 +5933,7 @@
         <v>10495</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>222</v>
       </c>
@@ -5972,7 +5947,7 @@
         <v>10502</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>223</v>
       </c>
@@ -5986,7 +5961,7 @@
         <v>10477</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>224</v>
       </c>
@@ -6000,7 +5975,7 @@
         <v>10478</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>225</v>
       </c>
@@ -6014,7 +5989,7 @@
         <v>10506</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>226</v>
       </c>
@@ -6028,7 +6003,7 @@
         <v>10474</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>227</v>
       </c>
@@ -6042,7 +6017,7 @@
         <v>10509</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>228</v>
       </c>
@@ -6056,7 +6031,7 @@
         <v>10498</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>229</v>
       </c>
@@ -6070,7 +6045,7 @@
         <v>10516</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>230</v>
       </c>
@@ -6084,7 +6059,7 @@
         <v>10507</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>231</v>
       </c>
@@ -6098,7 +6073,7 @@
         <v>10496</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>232</v>
       </c>
@@ -6112,7 +6087,7 @@
         <v>10512</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>233</v>
       </c>
@@ -6126,7 +6101,7 @@
         <v>10505</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>234</v>
       </c>
@@ -6140,7 +6115,7 @@
         <v>10511</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>235</v>
       </c>
@@ -6154,7 +6129,7 @@
         <v>10501</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>236</v>
       </c>
@@ -6168,7 +6143,7 @@
         <v>10518</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>237</v>
       </c>
@@ -6182,7 +6157,7 @@
         <v>10528</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>238</v>
       </c>
@@ -6196,7 +6171,7 @@
         <v>10503</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>239</v>
       </c>
@@ -6210,7 +6185,7 @@
         <v>10504</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>240</v>
       </c>
@@ -6224,7 +6199,7 @@
         <v>10523</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>241</v>
       </c>
@@ -6238,7 +6213,7 @@
         <v>10514</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>242</v>
       </c>
@@ -6252,7 +6227,7 @@
         <v>10510</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>243</v>
       </c>
@@ -6266,7 +6241,7 @@
         <v>10513</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>244</v>
       </c>
@@ -6280,7 +6255,7 @@
         <v>10508</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>245</v>
       </c>
@@ -6294,7 +6269,7 @@
         <v>10515</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>246</v>
       </c>
@@ -6308,7 +6283,7 @@
         <v>10531</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>247</v>
       </c>
@@ -6322,7 +6297,7 @@
         <v>10517</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>248</v>
       </c>
@@ -6336,7 +6311,7 @@
         <v>10533</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>249</v>
       </c>
@@ -6350,7 +6325,7 @@
         <v>10520</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>250</v>
       </c>
@@ -6364,7 +6339,7 @@
         <v>10527</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>251</v>
       </c>
@@ -6378,7 +6353,7 @@
         <v>10522</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>252</v>
       </c>
@@ -6392,7 +6367,7 @@
         <v>10541</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>253</v>
       </c>
@@ -6406,7 +6381,7 @@
         <v>10539</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>254</v>
       </c>
@@ -6420,7 +6395,7 @@
         <v>10542</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>255</v>
       </c>
@@ -6434,7 +6409,7 @@
         <v>10519</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>256</v>
       </c>
@@ -6448,7 +6423,7 @@
         <v>10550</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>257</v>
       </c>
@@ -6462,7 +6437,7 @@
         <v>10521</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>258</v>
       </c>
@@ -6476,7 +6451,7 @@
         <v>10543</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>259</v>
       </c>
@@ -6490,7 +6465,7 @@
         <v>10524</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>260</v>
       </c>
@@ -6504,7 +6479,7 @@
         <v>10525</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>261</v>
       </c>
@@ -6518,7 +6493,7 @@
         <v>10535</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>262</v>
       </c>
@@ -6532,7 +6507,7 @@
         <v>10534</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>263</v>
       </c>
@@ -6546,7 +6521,7 @@
         <v>10536</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>264</v>
       </c>
@@ -6560,7 +6535,7 @@
         <v>10526</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>265</v>
       </c>
@@ -6574,7 +6549,7 @@
         <v>10547</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>266</v>
       </c>
@@ -6588,7 +6563,7 @@
         <v>10548</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>267</v>
       </c>
@@ -6602,7 +6577,7 @@
         <v>10529</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>268</v>
       </c>
@@ -6616,7 +6591,7 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>269</v>
       </c>
@@ -6630,7 +6605,7 @@
         <v>10546</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>270</v>
       </c>
@@ -6644,7 +6619,7 @@
         <v>10549</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>271</v>
       </c>
@@ -6658,7 +6633,7 @@
         <v>10530</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>272</v>
       </c>
@@ -6672,7 +6647,7 @@
         <v>10544</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>273</v>
       </c>
@@ -6686,7 +6661,7 @@
         <v>10552</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>274</v>
       </c>
@@ -6700,7 +6675,7 @@
         <v>10532</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>275</v>
       </c>
@@ -6714,7 +6689,7 @@
         <v>10559</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>276</v>
       </c>
@@ -6728,7 +6703,7 @@
         <v>10564</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>277</v>
       </c>
@@ -6742,7 +6717,7 @@
         <v>10537</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>278</v>
       </c>
@@ -6756,7 +6731,7 @@
         <v>10568</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>279</v>
       </c>
@@ -6770,7 +6745,7 @@
         <v>10538</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>280</v>
       </c>
@@ -6784,7 +6759,7 @@
         <v>10551</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>281</v>
       </c>
@@ -6798,7 +6773,7 @@
         <v>10555</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>282</v>
       </c>
@@ -6812,7 +6787,7 @@
         <v>10545</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>283</v>
       </c>
@@ -6826,7 +6801,7 @@
         <v>10567</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>284</v>
       </c>
@@ -6840,7 +6815,7 @@
         <v>10576</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>285</v>
       </c>
@@ -6854,7 +6829,7 @@
         <v>10557</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>286</v>
       </c>
@@ -6868,7 +6843,7 @@
         <v>10562</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>287</v>
       </c>
@@ -6882,7 +6857,7 @@
         <v>10566</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>288</v>
       </c>
@@ -6896,7 +6871,7 @@
         <v>10554</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>289</v>
       </c>
@@ -6910,7 +6885,7 @@
         <v>10574</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>290</v>
       </c>
@@ -6924,7 +6899,7 @@
         <v>10575</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>291</v>
       </c>
@@ -6938,7 +6913,7 @@
         <v>10587</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>292</v>
       </c>
@@ -6952,7 +6927,7 @@
         <v>10553</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>293</v>
       </c>
@@ -6966,7 +6941,7 @@
         <v>10563</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>294</v>
       </c>
@@ -6980,7 +6955,7 @@
         <v>10571</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>295</v>
       </c>
@@ -6994,7 +6969,7 @@
         <v>10556</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>296</v>
       </c>
@@ -7008,7 +6983,7 @@
         <v>10565</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>297</v>
       </c>
@@ -7022,7 +6997,7 @@
         <v>10578</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>298</v>
       </c>
@@ -7036,7 +7011,7 @@
         <v>10580</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>299</v>
       </c>
@@ -7050,7 +7025,7 @@
         <v>10584</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>300</v>
       </c>
@@ -7064,7 +7039,7 @@
         <v>10558</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>301</v>
       </c>
@@ -7078,7 +7053,7 @@
         <v>10561</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>302</v>
       </c>
@@ -7092,7 +7067,7 @@
         <v>10595</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>303</v>
       </c>
@@ -7106,7 +7081,7 @@
         <v>10586</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>304</v>
       </c>
@@ -7120,7 +7095,7 @@
         <v>10579</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>305</v>
       </c>
@@ -7134,7 +7109,7 @@
         <v>10573</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>306</v>
       </c>
@@ -7148,7 +7123,7 @@
         <v>10593</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>307</v>
       </c>
@@ -7162,7 +7137,7 @@
         <v>10572</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>308</v>
       </c>
@@ -7176,7 +7151,7 @@
         <v>10577</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>309</v>
       </c>
@@ -7190,7 +7165,7 @@
         <v>10599</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>310</v>
       </c>
@@ -7204,7 +7179,7 @@
         <v>10594</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>311</v>
       </c>
@@ -7218,7 +7193,7 @@
         <v>10597</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>312</v>
       </c>
@@ -7232,7 +7207,7 @@
         <v>10581</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>313</v>
       </c>
@@ -7246,7 +7221,7 @@
         <v>10598</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>314</v>
       </c>
@@ -7260,7 +7235,7 @@
         <v>10582</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>315</v>
       </c>
@@ -7274,7 +7249,7 @@
         <v>10583</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>316</v>
       </c>
@@ -7288,7 +7263,7 @@
         <v>10611</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>317</v>
       </c>
@@ -7302,7 +7277,7 @@
         <v>10606</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>318</v>
       </c>
@@ -7316,7 +7291,7 @@
         <v>10585</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>319</v>
       </c>
@@ -7330,7 +7305,7 @@
         <v>10600</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>320</v>
       </c>
@@ -7344,7 +7319,7 @@
         <v>10592</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>321</v>
       </c>
@@ -7358,7 +7333,7 @@
         <v>10590</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>322</v>
       </c>
@@ -7372,7 +7347,7 @@
         <v>10610</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>323</v>
       </c>
@@ -7386,7 +7361,7 @@
         <v>10608</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>324</v>
       </c>
@@ -7400,7 +7375,7 @@
         <v>10623</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>325</v>
       </c>
@@ -7414,7 +7389,7 @@
         <v>10591</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>326</v>
       </c>
@@ -7428,7 +7403,7 @@
         <v>10625</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>327</v>
       </c>
@@ -7442,7 +7417,7 @@
         <v>10624</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>328</v>
       </c>
@@ -7456,7 +7431,7 @@
         <v>10596</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>329</v>
       </c>
@@ -7470,7 +7445,7 @@
         <v>10604</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>330</v>
       </c>
@@ -7484,7 +7459,7 @@
         <v>10602</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>331</v>
       </c>
@@ -7498,7 +7473,7 @@
         <v>10601</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>332</v>
       </c>
@@ -7512,7 +7487,7 @@
         <v>10630</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>333</v>
       </c>
@@ -7526,7 +7501,7 @@
         <v>10609</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>334</v>
       </c>
@@ -7540,7 +7515,7 @@
         <v>10629</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>335</v>
       </c>
@@ -7554,7 +7529,7 @@
         <v>10603</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>336</v>
       </c>
@@ -7568,7 +7543,7 @@
         <v>10634</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>337</v>
       </c>
@@ -7582,7 +7557,7 @@
         <v>10615</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>338</v>
       </c>
@@ -7596,7 +7571,7 @@
         <v>10617</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>339</v>
       </c>
@@ -7610,7 +7585,7 @@
         <v>10605</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>340</v>
       </c>
@@ -7624,7 +7599,7 @@
         <v>10613</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>341</v>
       </c>
@@ -7638,7 +7613,7 @@
         <v>10626</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>342</v>
       </c>
@@ -7652,7 +7627,7 @@
         <v>10635</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>343</v>
       </c>
@@ -7666,7 +7641,7 @@
         <v>10614</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>344</v>
       </c>
@@ -7680,7 +7655,7 @@
         <v>10618</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>345</v>
       </c>
@@ -7694,7 +7669,7 @@
         <v>10638</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>346</v>
       </c>
@@ -7708,7 +7683,7 @@
         <v>10645</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>347</v>
       </c>
@@ -7722,7 +7697,7 @@
         <v>10612</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>348</v>
       </c>
@@ -7736,7 +7711,7 @@
         <v>10622</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>349</v>
       </c>
@@ -7750,7 +7725,7 @@
         <v>10642</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>350</v>
       </c>
@@ -7764,7 +7739,7 @@
         <v>10651</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>351</v>
       </c>
@@ -7778,7 +7753,7 @@
         <v>10636</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>352</v>
       </c>
@@ -7792,7 +7767,7 @@
         <v>10619</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>353</v>
       </c>
@@ -7806,7 +7781,7 @@
         <v>10627</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>354</v>
       </c>
@@ -7820,7 +7795,7 @@
         <v>10641</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>355</v>
       </c>
@@ -7834,7 +7809,7 @@
         <v>10620</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>356</v>
       </c>
@@ -7848,7 +7823,7 @@
         <v>10621</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>357</v>
       </c>
@@ -7862,7 +7837,7 @@
         <v>10648</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>358</v>
       </c>
@@ -7876,7 +7851,7 @@
         <v>10654</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>359</v>
       </c>
@@ -7890,7 +7865,7 @@
         <v>10656</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>360</v>
       </c>
@@ -7904,7 +7879,7 @@
         <v>10628</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>361</v>
       </c>
@@ -7918,7 +7893,7 @@
         <v>10644</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>362</v>
       </c>
@@ -7932,7 +7907,7 @@
         <v>10631</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>363</v>
       </c>
@@ -7946,7 +7921,7 @@
         <v>10633</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>364</v>
       </c>
@@ -7960,7 +7935,7 @@
         <v>10650</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>365</v>
       </c>
@@ -7974,7 +7949,7 @@
         <v>10637</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>366</v>
       </c>
@@ -7988,7 +7963,7 @@
         <v>10647</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>367</v>
       </c>
@@ -8002,7 +7977,7 @@
         <v>10657</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>368</v>
       </c>
@@ -8016,7 +7991,7 @@
         <v>10632</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>369</v>
       </c>
@@ -8030,7 +8005,7 @@
         <v>10643</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>370</v>
       </c>
@@ -8044,7 +8019,7 @@
         <v>10671</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>371</v>
       </c>
@@ -8058,7 +8033,7 @@
         <v>10640</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>372</v>
       </c>
@@ -8072,7 +8047,7 @@
         <v>10665</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>373</v>
       </c>
@@ -8086,7 +8061,7 @@
         <v>10668</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>374</v>
       </c>
@@ -8100,7 +8075,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>375</v>
       </c>
@@ -8114,7 +8089,7 @@
         <v>10653</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>376</v>
       </c>
@@ -8128,7 +8103,7 @@
         <v>10664</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>377</v>
       </c>
@@ -8142,7 +8117,7 @@
         <v>10670</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>378</v>
       </c>
@@ -8156,7 +8131,7 @@
         <v>10677</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>379</v>
       </c>
@@ -8170,7 +8145,7 @@
         <v>10639</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>380</v>
       </c>
@@ -8184,7 +8159,7 @@
         <v>10661</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>381</v>
       </c>
@@ -8198,7 +8173,7 @@
         <v>10646</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>382</v>
       </c>
@@ -8212,7 +8187,7 @@
         <v>10660</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>383</v>
       </c>
@@ -8226,7 +8201,7 @@
         <v>10678</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>384</v>
       </c>
@@ -8240,7 +8215,7 @@
         <v>10676</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>385</v>
       </c>
@@ -8254,7 +8229,7 @@
         <v>10655</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>386</v>
       </c>
@@ -8268,7 +8243,7 @@
         <v>10684</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>387</v>
       </c>
@@ -8282,7 +8257,7 @@
         <v>10686</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>388</v>
       </c>
@@ -8296,7 +8271,7 @@
         <v>10669</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>389</v>
       </c>
@@ -8310,7 +8285,7 @@
         <v>10683</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>390</v>
       </c>
@@ -8324,7 +8299,7 @@
         <v>10649</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>391</v>
       </c>
@@ -8338,7 +8313,7 @@
         <v>10673</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>392</v>
       </c>
@@ -8352,7 +8327,7 @@
         <v>10659</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>393</v>
       </c>
@@ -8366,7 +8341,7 @@
         <v>10689</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>394</v>
       </c>
@@ -8380,7 +8355,7 @@
         <v>10682</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>395</v>
       </c>
@@ -8394,7 +8369,7 @@
         <v>10695</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>396</v>
       </c>
@@ -8408,7 +8383,7 @@
         <v>10652</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>397</v>
       </c>
@@ -8422,7 +8397,7 @@
         <v>10658</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>398</v>
       </c>
@@ -8436,7 +8411,7 @@
         <v>10679</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>399</v>
       </c>
@@ -8450,7 +8425,7 @@
         <v>10662</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>400</v>
       </c>
@@ -8464,7 +8439,7 @@
         <v>10663</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>401</v>
       </c>
@@ -8478,7 +8453,7 @@
         <v>10674</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>402</v>
       </c>
@@ -8492,7 +8467,7 @@
         <v>10667</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>403</v>
       </c>
@@ -8506,7 +8481,7 @@
         <v>10666</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>404</v>
       </c>
@@ -8520,7 +8495,7 @@
         <v>10700</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>405</v>
       </c>
@@ -8534,7 +8509,7 @@
         <v>10675</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>406</v>
       </c>
@@ -8548,7 +8523,7 @@
         <v>10681</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>407</v>
       </c>
@@ -8562,7 +8537,7 @@
         <v>10691</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>408</v>
       </c>
@@ -8576,7 +8551,7 @@
         <v>10693</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>409</v>
       </c>
@@ -8590,7 +8565,7 @@
         <v>10685</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>410</v>
       </c>
@@ -8604,7 +8579,7 @@
         <v>10692</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>411</v>
       </c>
@@ -8618,7 +8593,7 @@
         <v>10680</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>412</v>
       </c>
@@ -8632,7 +8607,7 @@
         <v>10706</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>413</v>
       </c>
@@ -8646,7 +8621,7 @@
         <v>10688</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>414</v>
       </c>
@@ -8660,7 +8635,7 @@
         <v>10702</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>415</v>
       </c>
@@ -8674,7 +8649,7 @@
         <v>10703</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>416</v>
       </c>
@@ -8688,7 +8663,7 @@
         <v>10715</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>417</v>
       </c>
@@ -8702,7 +8677,7 @@
         <v>10687</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>418</v>
       </c>
@@ -8716,7 +8691,7 @@
         <v>10696</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>419</v>
       </c>
@@ -8730,7 +8705,7 @@
         <v>10720</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>420</v>
       </c>
@@ -8744,7 +8719,7 @@
         <v>10697</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>421</v>
       </c>
@@ -8758,7 +8733,7 @@
         <v>10690</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>422</v>
       </c>
@@ -8772,7 +8747,7 @@
         <v>10725</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>423</v>
       </c>
@@ -8786,7 +8761,7 @@
         <v>10710</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>424</v>
       </c>
@@ -8800,7 +8775,7 @@
         <v>10726</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>425</v>
       </c>
@@ -8814,7 +8789,7 @@
         <v>10699</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>426</v>
       </c>
@@ -8828,7 +8803,7 @@
         <v>10718</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>427</v>
       </c>
@@ -8842,7 +8817,7 @@
         <v>10708</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>428</v>
       </c>
@@ -8856,7 +8831,7 @@
         <v>10716</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>429</v>
       </c>
@@ -8870,7 +8845,7 @@
         <v>10717</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>430</v>
       </c>
@@ -8884,7 +8859,7 @@
         <v>10701</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>431</v>
       </c>
@@ -8898,7 +8873,7 @@
         <v>10722</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>432</v>
       </c>
@@ -8912,7 +8887,7 @@
         <v>10723</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>433</v>
       </c>
@@ -8926,7 +8901,7 @@
         <v>10712</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>434</v>
       </c>
@@ -8940,7 +8915,7 @@
         <v>10707</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>435</v>
       </c>
@@ -8954,7 +8929,7 @@
         <v>10705</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>436</v>
       </c>
@@ -8968,7 +8943,7 @@
         <v>10730</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>437</v>
       </c>
@@ -8982,7 +8957,7 @@
         <v>10704</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>438</v>
       </c>
@@ -8996,7 +8971,7 @@
         <v>10709</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>439</v>
       </c>
@@ -9010,7 +8985,7 @@
         <v>10721</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>440</v>
       </c>
@@ -9024,7 +8999,7 @@
         <v>10737</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>441</v>
       </c>
@@ -9038,7 +9013,7 @@
         <v>10740</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>442</v>
       </c>
@@ -9052,7 +9027,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>443</v>
       </c>
@@ -9066,7 +9041,7 @@
         <v>10714</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>444</v>
       </c>
@@ -9080,7 +9055,7 @@
         <v>10711</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>445</v>
       </c>
@@ -9094,7 +9069,7 @@
         <v>10743</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>446</v>
       </c>
@@ -9108,7 +9083,7 @@
         <v>10729</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>447</v>
       </c>
@@ -9122,7 +9097,7 @@
         <v>10719</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>448</v>
       </c>
@@ -9136,7 +9111,7 @@
         <v>10735</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>449</v>
       </c>
@@ -9150,7 +9125,7 @@
         <v>10724</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>450</v>
       </c>
@@ -9164,7 +9139,7 @@
         <v>10738</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>451</v>
       </c>
@@ -9178,7 +9153,7 @@
         <v>10741</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>452</v>
       </c>
@@ -9192,7 +9167,7 @@
         <v>10744</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>453</v>
       </c>
@@ -9206,7 +9181,7 @@
         <v>10731</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>454</v>
       </c>
@@ -9220,7 +9195,7 @@
         <v>10750</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>455</v>
       </c>
@@ -9234,7 +9209,7 @@
         <v>10728</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>456</v>
       </c>
@@ -9248,7 +9223,7 @@
         <v>10734</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>457</v>
       </c>
@@ -9262,7 +9237,7 @@
         <v>10747</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>458</v>
       </c>
@@ -9276,7 +9251,7 @@
         <v>10757</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>459</v>
       </c>
@@ -9290,7 +9265,7 @@
         <v>10751</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>460</v>
       </c>
@@ -9304,7 +9279,7 @@
         <v>10746</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>461</v>
       </c>
@@ -9318,7 +9293,7 @@
         <v>10761</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>462</v>
       </c>
@@ -9332,7 +9307,7 @@
         <v>10733</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>463</v>
       </c>
@@ -9346,7 +9321,7 @@
         <v>10765</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>464</v>
       </c>
@@ -9360,7 +9335,7 @@
         <v>10736</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>465</v>
       </c>
@@ -9374,7 +9349,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>466</v>
       </c>
@@ -9388,7 +9363,7 @@
         <v>10767</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>467</v>
       </c>
@@ -9402,7 +9377,7 @@
         <v>10745</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>468</v>
       </c>
@@ -9416,7 +9391,7 @@
         <v>10742</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>469</v>
       </c>
@@ -9430,7 +9405,7 @@
         <v>10756</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>470</v>
       </c>
@@ -9444,7 +9419,7 @@
         <v>10752</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>471</v>
       </c>
@@ -9458,7 +9433,7 @@
         <v>10760</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>472</v>
       </c>
@@ -9472,7 +9447,7 @@
         <v>10776</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>473</v>
       </c>
@@ -9486,7 +9461,7 @@
         <v>10753</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>474</v>
       </c>
@@ -9500,7 +9475,7 @@
         <v>10768</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>475</v>
       </c>
@@ -9514,7 +9489,7 @@
         <v>10754</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>476</v>
       </c>
@@ -9528,7 +9503,7 @@
         <v>10739</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>477</v>
       </c>
@@ -9542,7 +9517,7 @@
         <v>10779</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>478</v>
       </c>
@@ -9556,7 +9531,7 @@
         <v>10755</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>479</v>
       </c>
@@ -9570,7 +9545,7 @@
         <v>10759</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>480</v>
       </c>
@@ -9584,7 +9559,7 @@
         <v>10784</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>481</v>
       </c>
@@ -9598,7 +9573,7 @@
         <v>10748</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>482</v>
       </c>
@@ -9612,7 +9587,7 @@
         <v>10789</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>483</v>
       </c>
@@ -9626,7 +9601,7 @@
         <v>10749</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>484</v>
       </c>
@@ -9640,7 +9615,7 @@
         <v>10781</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>485</v>
       </c>
@@ -9654,7 +9629,7 @@
         <v>10771</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>486</v>
       </c>
@@ -9668,7 +9643,7 @@
         <v>10774</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>487</v>
       </c>
@@ -9682,7 +9657,7 @@
         <v>10762</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>488</v>
       </c>
@@ -9696,7 +9671,7 @@
         <v>10770</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>489</v>
       </c>
@@ -9710,7 +9685,7 @@
         <v>10764</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>490</v>
       </c>
@@ -9724,7 +9699,7 @@
         <v>10766</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>491</v>
       </c>
@@ -9738,7 +9713,7 @@
         <v>10797</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>492</v>
       </c>
@@ -9752,7 +9727,7 @@
         <v>10763</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>493</v>
       </c>
@@ -9766,7 +9741,7 @@
         <v>10782</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>494</v>
       </c>
@@ -9780,7 +9755,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>495</v>
       </c>
@@ -9794,7 +9769,7 @@
         <v>10769</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>496</v>
       </c>
@@ -9808,7 +9783,7 @@
         <v>10778</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>497</v>
       </c>
@@ -9822,7 +9797,7 @@
         <v>10772</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>498</v>
       </c>
@@ -9836,7 +9811,7 @@
         <v>10790</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>499</v>
       </c>
@@ -9850,7 +9825,7 @@
         <v>10794</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>500</v>
       </c>
@@ -9864,7 +9839,7 @@
         <v>10807</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>501</v>
       </c>
@@ -9878,7 +9853,7 @@
         <v>10773</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>502</v>
       </c>
@@ -9892,7 +9867,7 @@
         <v>10802</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>503</v>
       </c>
@@ -9906,7 +9881,7 @@
         <v>10785</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>504</v>
       </c>
@@ -9920,7 +9895,7 @@
         <v>10808</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>505</v>
       </c>
@@ -9934,7 +9909,7 @@
         <v>10786</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>506</v>
       </c>
@@ -9948,7 +9923,7 @@
         <v>10810</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>507</v>
       </c>
@@ -9962,7 +9937,7 @@
         <v>10791</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>508</v>
       </c>
@@ -9976,7 +9951,7 @@
         <v>10809</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>509</v>
       </c>
@@ -9990,7 +9965,7 @@
         <v>10780</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>510</v>
       </c>
@@ -10004,7 +9979,7 @@
         <v>10777</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>511</v>
       </c>
@@ -10018,7 +9993,7 @@
         <v>10800</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>512</v>
       </c>
@@ -10032,7 +10007,7 @@
         <v>10816</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>513</v>
       </c>
@@ -10046,7 +10021,7 @@
         <v>10813</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>514</v>
       </c>
@@ -10060,7 +10035,7 @@
         <v>10798</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>515</v>
       </c>
@@ -10074,7 +10049,7 @@
         <v>10792</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>516</v>
       </c>
@@ -10088,7 +10063,7 @@
         <v>10803</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>517</v>
       </c>
@@ -10102,7 +10077,7 @@
         <v>10788</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>518</v>
       </c>
@@ -10116,7 +10091,7 @@
         <v>10795</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>519</v>
       </c>
@@ -10130,7 +10105,7 @@
         <v>10827</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>520</v>
       </c>
@@ -10144,7 +10119,7 @@
         <v>10805</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>521</v>
       </c>
@@ -10158,7 +10133,7 @@
         <v>10828</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>522</v>
       </c>
@@ -10172,7 +10147,7 @@
         <v>10796</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>523</v>
       </c>
@@ -10186,7 +10161,7 @@
         <v>10831</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>524</v>
       </c>
@@ -10200,7 +10175,7 @@
         <v>10793</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>525</v>
       </c>
@@ -10214,7 +10189,7 @@
         <v>10806</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>526</v>
       </c>
@@ -10228,7 +10203,7 @@
         <v>10799</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>527</v>
       </c>
@@ -10242,7 +10217,7 @@
         <v>10804</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>528</v>
       </c>
@@ -10256,7 +10231,7 @@
         <v>10801</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>529</v>
       </c>
@@ -10270,7 +10245,7 @@
         <v>10814</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>530</v>
       </c>
@@ -10284,7 +10259,7 @@
         <v>10840</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>531</v>
       </c>
@@ -10298,7 +10273,7 @@
         <v>10811</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>532</v>
       </c>
@@ -10312,7 +10287,7 @@
         <v>10821</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>533</v>
       </c>
@@ -10326,7 +10301,7 @@
         <v>10839</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>534</v>
       </c>
@@ -10340,7 +10315,7 @@
         <v>10818</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>535</v>
       </c>
@@ -10354,7 +10329,7 @@
         <v>10820</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>536</v>
       </c>
@@ -10368,7 +10343,7 @@
         <v>10832</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>537</v>
       </c>
@@ -10382,7 +10357,7 @@
         <v>10844</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>538</v>
       </c>
@@ -10396,7 +10371,7 @@
         <v>10817</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>539</v>
       </c>
@@ -10410,7 +10385,7 @@
         <v>10825</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>540</v>
       </c>
@@ -10424,7 +10399,7 @@
         <v>10812</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>541</v>
       </c>
@@ -10438,7 +10413,7 @@
         <v>10836</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>542</v>
       </c>
@@ -10452,7 +10427,7 @@
         <v>10845</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>543</v>
       </c>
@@ -10466,7 +10441,7 @@
         <v>10815</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>544</v>
       </c>
@@ -10480,7 +10455,7 @@
         <v>10819</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>545</v>
       </c>
@@ -10494,7 +10469,7 @@
         <v>10822</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>546</v>
       </c>
@@ -10508,7 +10483,7 @@
         <v>10823</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>547</v>
       </c>
@@ -10522,7 +10497,7 @@
         <v>10835</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>548</v>
       </c>
@@ -10536,7 +10511,7 @@
         <v>10829</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>549</v>
       </c>
@@ -10550,7 +10525,7 @@
         <v>10838</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>550</v>
       </c>
@@ -10564,7 +10539,7 @@
         <v>10858</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>551</v>
       </c>
@@ -10578,7 +10553,7 @@
         <v>10833</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>552</v>
       </c>
@@ -10592,7 +10567,7 @@
         <v>10861</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>553</v>
       </c>
@@ -10606,7 +10581,7 @@
         <v>10826</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>554</v>
       </c>
@@ -10620,7 +10595,7 @@
         <v>10824</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>555</v>
       </c>
@@ -10634,7 +10609,7 @@
         <v>10856</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>556</v>
       </c>
@@ -10648,7 +10623,7 @@
         <v>10860</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>557</v>
       </c>
@@ -10662,7 +10637,7 @@
         <v>10843</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>558</v>
       </c>
@@ -10676,7 +10651,7 @@
         <v>10837</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>559</v>
       </c>
@@ -10690,7 +10665,7 @@
         <v>10847</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>560</v>
       </c>
@@ -10704,7 +10679,7 @@
         <v>10855</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>561</v>
       </c>
@@ -10718,7 +10693,7 @@
         <v>10850</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>562</v>
       </c>
@@ -10732,7 +10707,7 @@
         <v>10849</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>563</v>
       </c>
@@ -10746,7 +10721,7 @@
         <v>10851</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>564</v>
       </c>
@@ -10760,7 +10735,7 @@
         <v>10852</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>565</v>
       </c>
@@ -10774,7 +10749,7 @@
         <v>10846</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>566</v>
       </c>
@@ -10788,7 +10763,7 @@
         <v>10848</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>567</v>
       </c>
@@ -10802,7 +10777,7 @@
         <v>10877</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>568</v>
       </c>
@@ -10816,7 +10791,7 @@
         <v>10883</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>569</v>
       </c>
@@ -10830,7 +10805,7 @@
         <v>10862</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>570</v>
       </c>
@@ -10844,7 +10819,7 @@
         <v>10857</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>571</v>
       </c>
@@ -10858,7 +10833,7 @@
         <v>10859</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>572</v>
       </c>
@@ -10872,7 +10847,7 @@
         <v>10879</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>573</v>
       </c>
@@ -10886,7 +10861,7 @@
         <v>10864</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>574</v>
       </c>
@@ -10900,7 +10875,7 @@
         <v>10854</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>575</v>
       </c>
@@ -10914,7 +10889,7 @@
         <v>10880</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>576</v>
       </c>
@@ -10928,7 +10903,7 @@
         <v>10881</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>577</v>
       </c>
@@ -10942,7 +10917,7 @@
         <v>10874</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>578</v>
       </c>
@@ -10956,7 +10931,7 @@
         <v>10863</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>579</v>
       </c>
@@ -10970,7 +10945,7 @@
         <v>10853</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>580</v>
       </c>
@@ -10984,7 +10959,7 @@
         <v>10875</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>581</v>
       </c>
@@ -10998,7 +10973,7 @@
         <v>10871</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>582</v>
       </c>
@@ -11012,7 +10987,7 @@
         <v>10867</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>583</v>
       </c>
@@ -11026,7 +11001,7 @@
         <v>10866</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>584</v>
       </c>
@@ -11040,7 +11015,7 @@
         <v>10897</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>585</v>
       </c>
@@ -11054,7 +11029,7 @@
         <v>10885</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>586</v>
       </c>
@@ -11068,7 +11043,7 @@
         <v>10896</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>587</v>
       </c>
@@ -11082,7 +11057,7 @@
         <v>10892</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>588</v>
       </c>
@@ -11096,7 +11071,7 @@
         <v>10868</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>589</v>
       </c>
@@ -11110,7 +11085,7 @@
         <v>10886</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>590</v>
       </c>
@@ -11124,7 +11099,7 @@
         <v>10865</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>591</v>
       </c>
@@ -11138,7 +11113,7 @@
         <v>10890</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>592</v>
       </c>
@@ -11152,7 +11127,7 @@
         <v>10870</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>593</v>
       </c>
@@ -11166,7 +11141,7 @@
         <v>10873</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>594</v>
       </c>
@@ -11180,7 +11155,7 @@
         <v>10876</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>595</v>
       </c>
@@ -11194,7 +11169,7 @@
         <v>10878</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>596</v>
       </c>
@@ -11208,7 +11183,7 @@
         <v>10872</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>597</v>
       </c>
@@ -11222,7 +11197,7 @@
         <v>10869</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>598</v>
       </c>
@@ -11236,7 +11211,7 @@
         <v>10889</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>599</v>
       </c>
@@ -11250,7 +11225,7 @@
         <v>10901</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>600</v>
       </c>
@@ -11264,7 +11239,7 @@
         <v>10905</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>601</v>
       </c>
@@ -11278,7 +11253,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>602</v>
       </c>
@@ -11292,7 +11267,7 @@
         <v>10882</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>603</v>
       </c>
@@ -11306,7 +11281,7 @@
         <v>10893</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>604</v>
       </c>
@@ -11320,7 +11295,7 @@
         <v>10899</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>605</v>
       </c>
@@ -11334,7 +11309,7 @@
         <v>10891</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>606</v>
       </c>
@@ -11348,7 +11323,7 @@
         <v>10888</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>607</v>
       </c>
@@ -11362,7 +11337,7 @@
         <v>10895</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>608</v>
       </c>
@@ -11376,7 +11351,7 @@
         <v>10913</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>609</v>
       </c>
@@ -11390,7 +11365,7 @@
         <v>10898</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>610</v>
       </c>
@@ -11404,7 +11379,7 @@
         <v>10906</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>611</v>
       </c>
@@ -11418,7 +11393,7 @@
         <v>10887</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>612</v>
       </c>
@@ -11432,7 +11407,7 @@
         <v>10884</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>613</v>
       </c>
@@ -11446,7 +11421,7 @@
         <v>10903</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>614</v>
       </c>
@@ -11460,7 +11435,7 @@
         <v>10922</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>615</v>
       </c>
@@ -11474,7 +11449,7 @@
         <v>10902</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>616</v>
       </c>
@@ -11488,7 +11463,7 @@
         <v>10904</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>617</v>
       </c>
@@ -11502,7 +11477,7 @@
         <v>10912</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>618</v>
       </c>
@@ -11516,7 +11491,7 @@
         <v>10894</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>619</v>
       </c>
@@ -11530,7 +11505,7 @@
         <v>10909</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>620</v>
       </c>
@@ -11544,7 +11519,7 @@
         <v>10926</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>621</v>
       </c>
@@ -11558,7 +11533,7 @@
         <v>10907</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>622</v>
       </c>
@@ -11572,7 +11547,7 @@
         <v>10917</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>623</v>
       </c>
@@ -11586,7 +11561,7 @@
         <v>10924</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>624</v>
       </c>
@@ -11600,7 +11575,7 @@
         <v>10927</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
         <v>625</v>
       </c>
@@ -11614,7 +11589,7 @@
         <v>10908</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>626</v>
       </c>
@@ -11628,7 +11603,7 @@
         <v>10920</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>627</v>
       </c>
@@ -11642,7 +11617,7 @@
         <v>10932</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
         <v>628</v>
       </c>
@@ -11656,7 +11631,7 @@
         <v>10916</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>629</v>
       </c>
@@ -11670,7 +11645,7 @@
         <v>10919</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>630</v>
       </c>
@@ -11684,7 +11659,7 @@
         <v>10938</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>631</v>
       </c>
@@ -11698,7 +11673,7 @@
         <v>10914</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>632</v>
       </c>
@@ -11712,7 +11687,7 @@
         <v>10910</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>633</v>
       </c>
@@ -11726,7 +11701,7 @@
         <v>10911</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>634</v>
       </c>
@@ -11740,7 +11715,7 @@
         <v>10934</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>635</v>
       </c>
@@ -11754,7 +11729,7 @@
         <v>10915</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>636</v>
       </c>
@@ -11768,7 +11743,7 @@
         <v>10930</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>637</v>
       </c>
@@ -11782,7 +11757,7 @@
         <v>10939</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>638</v>
       </c>
@@ -11796,7 +11771,7 @@
         <v>10946</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>639</v>
       </c>
@@ -11810,7 +11785,7 @@
         <v>10928</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>640</v>
       </c>
@@ -11824,7 +11799,7 @@
         <v>10921</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>641</v>
       </c>
@@ -11838,7 +11813,7 @@
         <v>10929</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>642</v>
       </c>
@@ -11852,7 +11827,7 @@
         <v>10925</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>643</v>
       </c>
@@ -11866,7 +11841,7 @@
         <v>10943</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>644</v>
       </c>
@@ -11880,7 +11855,7 @@
         <v>10953</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>645</v>
       </c>
@@ -11894,7 +11869,7 @@
         <v>10933</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>646</v>
       </c>
@@ -11908,7 +11883,7 @@
         <v>10918</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>647</v>
       </c>
@@ -11922,7 +11897,7 @@
         <v>10923</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>648</v>
       </c>
@@ -11936,7 +11911,7 @@
         <v>10931</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>649</v>
       </c>
@@ -11950,7 +11925,7 @@
         <v>10947</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>650</v>
       </c>
@@ -11964,7 +11939,7 @@
         <v>10944</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>651</v>
       </c>
@@ -11978,7 +11953,7 @@
         <v>10957</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>652</v>
       </c>
@@ -11992,7 +11967,7 @@
         <v>10963</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>653</v>
       </c>
@@ -12006,7 +11981,7 @@
         <v>10950</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
         <v>654</v>
       </c>
@@ -12020,7 +11995,7 @@
         <v>10962</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>655</v>
       </c>
@@ -12034,7 +12009,7 @@
         <v>10941</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
         <v>656</v>
       </c>
@@ -12048,7 +12023,7 @@
         <v>10935</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>657</v>
       </c>
@@ -12062,7 +12037,7 @@
         <v>10936</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>658</v>
       </c>
@@ -12076,7 +12051,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
         <v>659</v>
       </c>
@@ -12090,7 +12065,7 @@
         <v>10968</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>660</v>
       </c>
@@ -12104,7 +12079,7 @@
         <v>10956</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>661</v>
       </c>
@@ -12118,7 +12093,7 @@
         <v>10969</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>662</v>
       </c>
@@ -12132,7 +12107,7 @@
         <v>10942</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>663</v>
       </c>
@@ -12146,7 +12121,7 @@
         <v>10973</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>664</v>
       </c>
@@ -12160,7 +12135,7 @@
         <v>10974</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>665</v>
       </c>
@@ -12174,7 +12149,7 @@
         <v>10940</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>666</v>
       </c>
@@ -12188,7 +12163,7 @@
         <v>10961</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>667</v>
       </c>
@@ -12202,7 +12177,7 @@
         <v>10965</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>668</v>
       </c>
@@ -12216,7 +12191,7 @@
         <v>10954</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>669</v>
       </c>
@@ -12230,7 +12205,7 @@
         <v>10967</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>670</v>
       </c>
@@ -12244,7 +12219,7 @@
         <v>10972</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
         <v>671</v>
       </c>
@@ -12258,7 +12233,7 @@
         <v>10945</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>672</v>
       </c>
@@ -12272,7 +12247,7 @@
         <v>10952</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>673</v>
       </c>
@@ -12286,7 +12261,7 @@
         <v>10982</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>674</v>
       </c>
@@ -12300,7 +12275,7 @@
         <v>10981</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>675</v>
       </c>
@@ -12314,7 +12289,7 @@
         <v>10958</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>676</v>
       </c>
@@ -12328,7 +12303,7 @@
         <v>10964</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
         <v>677</v>
       </c>
@@ -12342,7 +12317,7 @@
         <v>10948</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>678</v>
       </c>
@@ -12356,7 +12331,7 @@
         <v>10975</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>679</v>
       </c>
@@ -12370,7 +12345,7 @@
         <v>10960</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>680</v>
       </c>
@@ -12384,7 +12359,7 @@
         <v>10977</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
         <v>681</v>
       </c>
@@ -12398,7 +12373,7 @@
         <v>10959</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>682</v>
       </c>
@@ -12412,7 +12387,7 @@
         <v>10978</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>683</v>
       </c>
@@ -12426,7 +12401,7 @@
         <v>10989</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>684</v>
       </c>
@@ -12440,7 +12415,7 @@
         <v>10976</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>685</v>
       </c>
@@ -12454,7 +12429,7 @@
         <v>10971</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>686</v>
       </c>
@@ -12468,7 +12443,7 @@
         <v>10986</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>687</v>
       </c>
@@ -12482,7 +12457,7 @@
         <v>10979</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>688</v>
       </c>
@@ -12496,7 +12471,7 @@
         <v>10985</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>689</v>
       </c>
@@ -12510,7 +12485,7 @@
         <v>10970</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>690</v>
       </c>
@@ -12524,7 +12499,7 @@
         <v>10966</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>691</v>
       </c>
@@ -12538,7 +12513,7 @@
         <v>11003</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>692</v>
       </c>
@@ -12552,7 +12527,7 @@
         <v>11004</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>693</v>
       </c>
@@ -12566,7 +12541,7 @@
         <v>10980</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
         <v>694</v>
       </c>
@@ -12580,7 +12555,7 @@
         <v>10992</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
         <v>695</v>
       </c>
@@ -12594,7 +12569,7 @@
         <v>10997</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
         <v>696</v>
       </c>
@@ -12608,7 +12583,7 @@
         <v>10984</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
         <v>697</v>
       </c>
@@ -12622,7 +12597,7 @@
         <v>10988</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
         <v>698</v>
       </c>
@@ -12636,7 +12611,7 @@
         <v>10987</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
         <v>699</v>
       </c>
@@ -12650,7 +12625,7 @@
         <v>10995</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
         <v>700</v>
       </c>
@@ -12664,7 +12639,7 @@
         <v>10996</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
         <v>701</v>
       </c>
@@ -12678,7 +12653,7 @@
         <v>11002</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
         <v>702</v>
       </c>
@@ -12692,7 +12667,7 @@
         <v>10983</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
         <v>703</v>
       </c>
@@ -12706,7 +12681,7 @@
         <v>11008</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
         <v>704</v>
       </c>
@@ -12720,7 +12695,7 @@
         <v>11005</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
         <v>705</v>
       </c>
@@ -12734,7 +12709,7 @@
         <v>10991</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
         <v>706</v>
       </c>
@@ -12748,7 +12723,7 @@
         <v>11007</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
         <v>707</v>
       </c>
@@ -12762,7 +12737,7 @@
         <v>10990</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
         <v>708</v>
       </c>
@@ -12776,7 +12751,7 @@
         <v>11022</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
         <v>709</v>
       </c>
@@ -12790,7 +12765,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
         <v>710</v>
       </c>
@@ -12804,7 +12779,7 @@
         <v>11021</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
         <v>711</v>
       </c>
@@ -12818,7 +12793,7 @@
         <v>11017</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
         <v>712</v>
       </c>
@@ -12832,7 +12807,7 @@
         <v>11013</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
         <v>713</v>
       </c>
@@ -12846,7 +12821,7 @@
         <v>11006</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
         <v>714</v>
       </c>
@@ -12860,7 +12835,7 @@
         <v>11016</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
         <v>715</v>
       </c>
@@ -12874,7 +12849,7 @@
         <v>11019</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
         <v>716</v>
       </c>
@@ -12888,7 +12863,7 @@
         <v>10994</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
         <v>717</v>
       </c>
@@ -12902,7 +12877,7 @@
         <v>11028</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
         <v>718</v>
       </c>
@@ -12916,7 +12891,7 @@
         <v>11023</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
         <v>719</v>
       </c>
@@ -12930,7 +12905,7 @@
         <v>11034</v>
       </c>
     </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
         <v>720</v>
       </c>
@@ -12944,7 +12919,7 @@
         <v>10999</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
         <v>721</v>
       </c>
@@ -12958,7 +12933,7 @@
         <v>10998</v>
       </c>
     </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
         <v>722</v>
       </c>
@@ -12972,7 +12947,7 @@
         <v>11036</v>
       </c>
     </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
         <v>723</v>
       </c>
@@ -12986,7 +12961,7 @@
         <v>11001</v>
       </c>
     </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
         <v>724</v>
       </c>
@@ -13000,7 +12975,7 @@
         <v>11015</v>
       </c>
     </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
         <v>725</v>
       </c>
@@ -13014,7 +12989,7 @@
         <v>11014</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
         <v>726</v>
       </c>
@@ -13028,7 +13003,7 @@
         <v>11031</v>
       </c>
     </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>727</v>
       </c>
@@ -13042,7 +13017,7 @@
         <v>11011</v>
       </c>
     </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>728</v>
       </c>
@@ -13056,7 +13031,7 @@
         <v>11009</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>729</v>
       </c>
@@ -13070,7 +13045,7 @@
         <v>11012</v>
       </c>
     </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
         <v>730</v>
       </c>
@@ -13084,7 +13059,7 @@
         <v>11010</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
         <v>731</v>
       </c>
@@ -13098,7 +13073,7 @@
         <v>11032</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
         <v>732</v>
       </c>
@@ -13112,7 +13087,7 @@
         <v>11035</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
         <v>733</v>
       </c>
@@ -13126,7 +13101,7 @@
         <v>11020</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
         <v>734</v>
       </c>
@@ -13140,7 +13115,7 @@
         <v>11018</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
         <v>735</v>
       </c>
@@ -13154,7 +13129,7 @@
         <v>11030</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
         <v>736</v>
       </c>
@@ -13168,7 +13143,7 @@
         <v>11042</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
         <v>737</v>
       </c>
@@ -13182,7 +13157,7 @@
         <v>11038</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
         <v>738</v>
       </c>
@@ -13196,7 +13171,7 @@
         <v>11051</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
         <v>739</v>
       </c>
@@ -13210,7 +13185,7 @@
         <v>11024</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
         <v>740</v>
       </c>
@@ -13224,7 +13199,7 @@
         <v>11027</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
         <v>741</v>
       </c>
@@ -13238,7 +13213,7 @@
         <v>11049</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
         <v>742</v>
       </c>
@@ -13252,7 +13227,7 @@
         <v>11053</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
         <v>743</v>
       </c>
@@ -13266,7 +13241,7 @@
         <v>11043</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
         <v>744</v>
       </c>
@@ -13280,7 +13255,7 @@
         <v>11047</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
         <v>745</v>
       </c>
@@ -13294,7 +13269,7 @@
         <v>11029</v>
       </c>
     </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
         <v>746</v>
       </c>
@@ -13308,7 +13283,7 @@
         <v>11057</v>
       </c>
     </row>
-    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
         <v>747</v>
       </c>
@@ -13322,7 +13297,7 @@
         <v>11033</v>
       </c>
     </row>
-    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
         <v>748</v>
       </c>
@@ -13336,7 +13311,7 @@
         <v>11058</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
         <v>749</v>
       </c>
@@ -13350,7 +13325,7 @@
         <v>11037</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
         <v>750</v>
       </c>
@@ -13364,7 +13339,7 @@
         <v>11044</v>
       </c>
     </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
         <v>751</v>
       </c>
@@ -13378,7 +13353,7 @@
         <v>11064</v>
       </c>
     </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
         <v>752</v>
       </c>
@@ -13392,7 +13367,7 @@
         <v>11039</v>
       </c>
     </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
         <v>753</v>
       </c>
@@ -13406,7 +13381,7 @@
         <v>11040</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
         <v>754</v>
       </c>
@@ -13420,7 +13395,7 @@
         <v>11052</v>
       </c>
     </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
         <v>755</v>
       </c>
@@ -13434,7 +13409,7 @@
         <v>11069</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
         <v>756</v>
       </c>
@@ -13448,7 +13423,7 @@
         <v>11059</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
         <v>757</v>
       </c>
@@ -13462,7 +13437,7 @@
         <v>11063</v>
       </c>
     </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A762" t="s">
         <v>758</v>
       </c>
@@ -13476,7 +13451,7 @@
         <v>11041</v>
       </c>
     </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A763" t="s">
         <v>759</v>
       </c>
@@ -13490,7 +13465,7 @@
         <v>11048</v>
       </c>
     </row>
-    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A764" t="s">
         <v>760</v>
       </c>
@@ -13504,7 +13479,7 @@
         <v>11050</v>
       </c>
     </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A765" t="s">
         <v>761</v>
       </c>
@@ -13518,7 +13493,7 @@
         <v>11066</v>
       </c>
     </row>
-    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A766" t="s">
         <v>762</v>
       </c>
@@ -13532,7 +13507,7 @@
         <v>11075</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A767" t="s">
         <v>763</v>
       </c>
@@ -13546,7 +13521,7 @@
         <v>11062</v>
       </c>
     </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A768" t="s">
         <v>764</v>
       </c>
@@ -13560,7 +13535,7 @@
         <v>11065</v>
       </c>
     </row>
-    <row r="769" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A769" t="s">
         <v>765</v>
       </c>
@@ -13574,7 +13549,7 @@
         <v>11061</v>
       </c>
     </row>
-    <row r="770" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A770" t="s">
         <v>766</v>
       </c>
@@ -13588,7 +13563,7 @@
         <v>11055</v>
       </c>
     </row>
-    <row r="771" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A771" t="s">
         <v>767</v>
       </c>
@@ -13602,7 +13577,7 @@
         <v>11054</v>
       </c>
     </row>
-    <row r="772" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A772" t="s">
         <v>768</v>
       </c>
@@ -13616,7 +13591,7 @@
         <v>11074</v>
       </c>
     </row>
-    <row r="773" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A773" t="s">
         <v>769</v>
       </c>
@@ -13630,7 +13605,7 @@
         <v>11067</v>
       </c>
     </row>
-    <row r="774" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A774" t="s">
         <v>770</v>
       </c>
@@ -13644,7 +13619,7 @@
         <v>11060</v>
       </c>
     </row>
-    <row r="775" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A775" t="s">
         <v>771</v>
       </c>
@@ -13658,7 +13633,7 @@
         <v>11071</v>
       </c>
     </row>
-    <row r="776" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A776" t="s">
         <v>772</v>
       </c>
@@ -13672,7 +13647,7 @@
         <v>11077</v>
       </c>
     </row>
-    <row r="777" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A777" t="s">
         <v>773</v>
       </c>
@@ -13686,7 +13661,7 @@
         <v>11068</v>
       </c>
     </row>
-    <row r="778" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A778" t="s">
         <v>774</v>
       </c>
@@ -13700,7 +13675,7 @@
         <v>11070</v>
       </c>
     </row>
-    <row r="779" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A779" t="s">
         <v>775</v>
       </c>
@@ -13714,7 +13689,7 @@
         <v>11073</v>
       </c>
     </row>
-    <row r="780" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A780" t="s">
         <v>776</v>
       </c>
